--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123037521</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123037521</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123037521</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,588 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127482964</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80021</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tjyvhällsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>656152</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6651917</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127482976</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjyvhällsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>656169</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6651943</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127482989</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91955</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjyvhällsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>656150</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6651952</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127482958</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjyvhällsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>656159</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6651918</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127482975</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjyvhällsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>656161</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6651948</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127482957</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjyvhällsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>656141</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6651952</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127482964</v>
       </c>
       <c r="B3" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91955</v>
+        <v>91959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92023</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127482964</v>
       </c>
       <c r="B3" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91959</v>
+        <v>91961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91961</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127482964</v>
       </c>
       <c r="B3" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>127482964</v>
       </c>
       <c r="B3" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
+        <v>91978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91978</v>
+        <v>91979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91979</v>
+        <v>91980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>127482976</v>
       </c>
       <c r="B4" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>127482989</v>
       </c>
       <c r="B5" t="n">
-        <v>91980</v>
+        <v>91981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127482958</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127482975</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127482957</v>
       </c>
       <c r="B8" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,2533 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129450135</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92863</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>656302</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6651806</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129450125</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>656478</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6651695</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129450143</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>656288</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6651998</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129450118</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96956</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>656384</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6651828</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129450149</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>656408</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6651894</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129450145</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>656489</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6651676</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129450147</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>656424</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6651882</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129450122</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96956</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>656463</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6651762</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129450126</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92261</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>656381</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6652003</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129450151</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>656360</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6652001</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129450181</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92193</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>656449</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6651818</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129450133</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91316</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>656452</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6651821</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129450141</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>656296</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6651986</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129450144</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>656452</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6651659</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129450152</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>656331</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6651995</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129450134</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>656478</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6651695</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129450182</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92193</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>656389</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6651977</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129450146</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>656452</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6651833</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129450128</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>656420</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6651730</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129450180</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>656460</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6651683</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129450140</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>656443</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6651673</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129450184</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>656281</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6652012</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129450150</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>656444</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6651992</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129450117</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96956</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>53</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>656462</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6651769</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129450119</v>
+      </c>
+      <c r="B33" t="n">
+        <v>96956</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>53</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>656298</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6651713</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129450148</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>656416</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6651889</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1755,7 +1755,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129450149</v>
+        <v>129450147</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656408</v>
+        <v>656424</v>
       </c>
       <c r="R13" t="n">
-        <v>6651894</v>
+        <v>6651882</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129450145</v>
+        <v>129450149</v>
       </c>
       <c r="B14" t="n">
         <v>4779</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656489</v>
+        <v>656408</v>
       </c>
       <c r="R14" t="n">
-        <v>6651676</v>
+        <v>6651894</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129450147</v>
+        <v>129450145</v>
       </c>
       <c r="B15" t="n">
         <v>4779</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656424</v>
+        <v>656489</v>
       </c>
       <c r="R15" t="n">
-        <v>6651882</v>
+        <v>6651676</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450181</v>
+        <v>129450133</v>
       </c>
       <c r="B19" t="n">
-        <v>92193</v>
+        <v>91316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656449</v>
+        <v>656452</v>
       </c>
       <c r="R19" t="n">
-        <v>6651818</v>
+        <v>6651821</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B20" t="n">
-        <v>91316</v>
+        <v>4779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R20" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>92193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B19" t="n">
-        <v>91316</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R19" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450141</v>
+        <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>4779</v>
+        <v>91318</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656296</v>
+        <v>656452</v>
       </c>
       <c r="R20" t="n">
-        <v>6651986</v>
+        <v>6651821</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2534,7 +2534,7 @@
         <v>129450181</v>
       </c>
       <c r="B21" t="n">
-        <v>92193</v>
+        <v>92195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129450144</v>
+        <v>129450152</v>
       </c>
       <c r="B22" t="n">
         <v>4779</v>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656452</v>
+        <v>656331</v>
       </c>
       <c r="R22" t="n">
-        <v>6651659</v>
+        <v>6651995</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129450152</v>
+        <v>129450144</v>
       </c>
       <c r="B23" t="n">
         <v>4779</v>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656331</v>
+        <v>656452</v>
       </c>
       <c r="R23" t="n">
-        <v>6651995</v>
+        <v>6651659</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2822,32 +2822,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129450134</v>
+        <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>92195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656478</v>
+        <v>656389</v>
       </c>
       <c r="R24" t="n">
-        <v>6651695</v>
+        <v>6651977</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2919,32 +2919,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129450182</v>
+        <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92193</v>
+        <v>91998</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656389</v>
+        <v>656478</v>
       </c>
       <c r="R25" t="n">
-        <v>6651977</v>
+        <v>6651695</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>80084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R27" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,6 +3184,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3210,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R28" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3281,11 +3286,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>4779</v>
+        <v>96958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R31" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B32" t="n">
-        <v>96956</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R32" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R19" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2437,7 +2437,7 @@
         <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450181</v>
+        <v>129450141</v>
       </c>
       <c r="B21" t="n">
-        <v>92195</v>
+        <v>4779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656449</v>
+        <v>656296</v>
       </c>
       <c r="R21" t="n">
-        <v>6651818</v>
+        <v>6651986</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2825,7 +2825,7 @@
         <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92195</v>
+        <v>92199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B27" t="n">
-        <v>80084</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R27" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,11 +3184,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3215,32 +3210,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>80084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R28" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3286,6 +3281,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,7 +3509,7 @@
         <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450181</v>
+        <v>129450133</v>
       </c>
       <c r="B19" t="n">
-        <v>92199</v>
+        <v>91323</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656449</v>
+        <v>656452</v>
       </c>
       <c r="R19" t="n">
-        <v>6651818</v>
+        <v>6651821</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450133</v>
+        <v>129450181</v>
       </c>
       <c r="B20" t="n">
-        <v>91322</v>
+        <v>92200</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656452</v>
+        <v>656449</v>
       </c>
       <c r="R20" t="n">
-        <v>6651821</v>
+        <v>6651818</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2825,7 +2825,7 @@
         <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92199</v>
+        <v>92200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>80084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R27" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,6 +3184,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3210,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B28" t="n">
-        <v>80084</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R28" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3281,11 +3286,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3509,7 +3509,7 @@
         <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B27" t="n">
-        <v>80084</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R27" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,11 +3184,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3215,32 +3210,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>80084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R28" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3286,6 +3281,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B31" t="n">
-        <v>96970</v>
+        <v>4779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R31" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>96970</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R32" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B19" t="n">
-        <v>91323</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R19" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450181</v>
+        <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>92200</v>
+        <v>91323</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656449</v>
+        <v>656452</v>
       </c>
       <c r="R20" t="n">
-        <v>6651818</v>
+        <v>6651821</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>92200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129450147</v>
+        <v>129450145</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656424</v>
+        <v>656489</v>
       </c>
       <c r="R13" t="n">
-        <v>6651882</v>
+        <v>6651676</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129450145</v>
+        <v>129450147</v>
       </c>
       <c r="B15" t="n">
         <v>4779</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656489</v>
+        <v>656424</v>
       </c>
       <c r="R15" t="n">
-        <v>6651676</v>
+        <v>6651882</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>129450181</v>
       </c>
       <c r="B21" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>80084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R27" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,6 +3184,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3210,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B28" t="n">
-        <v>80084</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R28" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3281,11 +3286,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129450140</v>
+        <v>129450184</v>
       </c>
       <c r="B29" t="n">
         <v>4779</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656443</v>
+        <v>656281</v>
       </c>
       <c r="R29" t="n">
-        <v>6651673</v>
+        <v>6652012</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129450184</v>
+        <v>129450140</v>
       </c>
       <c r="B30" t="n">
         <v>4779</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656281</v>
+        <v>656443</v>
       </c>
       <c r="R30" t="n">
-        <v>6652012</v>
+        <v>6651673</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>4779</v>
+        <v>96973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R31" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B32" t="n">
-        <v>96970</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R32" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1464,32 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450125</v>
+        <v>129450143</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R10" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450143</v>
+        <v>129450125</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656288</v>
+        <v>656478</v>
       </c>
       <c r="R11" t="n">
-        <v>6651998</v>
+        <v>6651695</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129450145</v>
+        <v>129450147</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656489</v>
+        <v>656424</v>
       </c>
       <c r="R13" t="n">
-        <v>6651676</v>
+        <v>6651882</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129450147</v>
+        <v>129450145</v>
       </c>
       <c r="B15" t="n">
         <v>4779</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656424</v>
+        <v>656489</v>
       </c>
       <c r="R15" t="n">
-        <v>6651882</v>
+        <v>6651676</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450141</v>
+        <v>129450133</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656296</v>
+        <v>656452</v>
       </c>
       <c r="R19" t="n">
-        <v>6651986</v>
+        <v>6651821</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450133</v>
+        <v>129450181</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>92203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656452</v>
+        <v>656449</v>
       </c>
       <c r="R20" t="n">
-        <v>6651821</v>
+        <v>6651818</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450181</v>
+        <v>129450141</v>
       </c>
       <c r="B21" t="n">
-        <v>92203</v>
+        <v>4779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656449</v>
+        <v>656296</v>
       </c>
       <c r="R21" t="n">
-        <v>6651818</v>
+        <v>6651986</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129450184</v>
+        <v>129450140</v>
       </c>
       <c r="B29" t="n">
         <v>4779</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656281</v>
+        <v>656443</v>
       </c>
       <c r="R29" t="n">
-        <v>6652012</v>
+        <v>6651673</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129450140</v>
+        <v>129450184</v>
       </c>
       <c r="B30" t="n">
         <v>4779</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656443</v>
+        <v>656281</v>
       </c>
       <c r="R30" t="n">
-        <v>6651673</v>
+        <v>6652012</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1464,32 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450143</v>
+        <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>91553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656288</v>
+        <v>656478</v>
       </c>
       <c r="R10" t="n">
-        <v>6651998</v>
+        <v>6651695</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450125</v>
+        <v>129450143</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R11" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R19" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450181</v>
+        <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>92203</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656449</v>
+        <v>656452</v>
       </c>
       <c r="R20" t="n">
-        <v>6651818</v>
+        <v>6651821</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>92203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92203</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R19" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450181</v>
+        <v>129450141</v>
       </c>
       <c r="B21" t="n">
-        <v>92203</v>
+        <v>4779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656449</v>
+        <v>656296</v>
       </c>
       <c r="R21" t="n">
-        <v>6651818</v>
+        <v>6651986</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1755,7 +1755,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129450147</v>
+        <v>129450145</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656424</v>
+        <v>656489</v>
       </c>
       <c r="R13" t="n">
-        <v>6651882</v>
+        <v>6651676</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129450145</v>
+        <v>129450147</v>
       </c>
       <c r="B15" t="n">
         <v>4779</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656489</v>
+        <v>656424</v>
       </c>
       <c r="R15" t="n">
-        <v>6651676</v>
+        <v>6651882</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450181</v>
+        <v>129450141</v>
       </c>
       <c r="B19" t="n">
-        <v>92203</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656449</v>
+        <v>656296</v>
       </c>
       <c r="R19" t="n">
-        <v>6651818</v>
+        <v>6651986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450133</v>
+        <v>129450181</v>
       </c>
       <c r="B20" t="n">
-        <v>91326</v>
+        <v>92203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656452</v>
+        <v>656449</v>
       </c>
       <c r="R20" t="n">
-        <v>6651821</v>
+        <v>6651818</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450133</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>91326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656452</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651821</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129450140</v>
+        <v>129450184</v>
       </c>
       <c r="B29" t="n">
         <v>4779</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656443</v>
+        <v>656281</v>
       </c>
       <c r="R29" t="n">
-        <v>6651673</v>
+        <v>6652012</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129450184</v>
+        <v>129450140</v>
       </c>
       <c r="B30" t="n">
         <v>4779</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656281</v>
+        <v>656443</v>
       </c>
       <c r="R30" t="n">
-        <v>6652012</v>
+        <v>6651673</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129450145</v>
+        <v>129450147</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656489</v>
+        <v>656424</v>
       </c>
       <c r="R13" t="n">
-        <v>6651676</v>
+        <v>6651882</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129450147</v>
+        <v>129450145</v>
       </c>
       <c r="B15" t="n">
         <v>4779</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656424</v>
+        <v>656489</v>
       </c>
       <c r="R15" t="n">
-        <v>6651882</v>
+        <v>6651676</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450141</v>
+        <v>129450133</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>91354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656296</v>
+        <v>656452</v>
       </c>
       <c r="R19" t="n">
-        <v>6651986</v>
+        <v>6651821</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2437,7 +2437,7 @@
         <v>129450181</v>
       </c>
       <c r="B20" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>4779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R21" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2825,7 +2825,7 @@
         <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>129450180</v>
       </c>
       <c r="B27" t="n">
-        <v>80084</v>
+        <v>80110</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>129450128</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129450184</v>
+        <v>129450140</v>
       </c>
       <c r="B29" t="n">
         <v>4779</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656281</v>
+        <v>656443</v>
       </c>
       <c r="R29" t="n">
-        <v>6652012</v>
+        <v>6651673</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129450140</v>
+        <v>129450184</v>
       </c>
       <c r="B30" t="n">
         <v>4779</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656443</v>
+        <v>656281</v>
       </c>
       <c r="R30" t="n">
-        <v>6651673</v>
+        <v>6652012</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B31" t="n">
-        <v>96973</v>
+        <v>4779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R31" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>97002</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R32" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1464,32 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450125</v>
+        <v>129450143</v>
       </c>
       <c r="B10" t="n">
-        <v>91581</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R10" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450143</v>
+        <v>129450125</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>91581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656288</v>
+        <v>656478</v>
       </c>
       <c r="R11" t="n">
-        <v>6651998</v>
+        <v>6651695</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>4779</v>
+        <v>97002</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R31" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B32" t="n">
-        <v>97002</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R32" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129450125</v>
       </c>
       <c r="B11" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450133</v>
+        <v>129450181</v>
       </c>
       <c r="B19" t="n">
-        <v>91354</v>
+        <v>92237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656452</v>
+        <v>656449</v>
       </c>
       <c r="R19" t="n">
-        <v>6651821</v>
+        <v>6651818</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450181</v>
+        <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>92231</v>
+        <v>91360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656449</v>
+        <v>656452</v>
       </c>
       <c r="R20" t="n">
-        <v>6651818</v>
+        <v>6651821</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2825,7 +2825,7 @@
         <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B27" t="n">
-        <v>80110</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R27" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,11 +3184,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3215,32 +3210,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B28" t="n">
-        <v>57890</v>
+        <v>80115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R28" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3286,6 +3281,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B31" t="n">
-        <v>97002</v>
+        <v>4779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R31" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>97014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R32" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129450125</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450181</v>
+        <v>129450141</v>
       </c>
       <c r="B19" t="n">
-        <v>92237</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656449</v>
+        <v>656296</v>
       </c>
       <c r="R19" t="n">
-        <v>6651818</v>
+        <v>6651986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2437,7 +2437,7 @@
         <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>92238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2822,32 +2822,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129450182</v>
+        <v>129450134</v>
       </c>
       <c r="B24" t="n">
-        <v>92237</v>
+        <v>92041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656389</v>
+        <v>656478</v>
       </c>
       <c r="R24" t="n">
-        <v>6651977</v>
+        <v>6651695</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2919,32 +2919,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129450134</v>
+        <v>129450182</v>
       </c>
       <c r="B25" t="n">
-        <v>92040</v>
+        <v>92238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656478</v>
+        <v>656389</v>
       </c>
       <c r="R25" t="n">
-        <v>6651695</v>
+        <v>6651977</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B27" t="n">
-        <v>57895</v>
+        <v>80116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R27" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,6 +3184,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3210,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B28" t="n">
-        <v>80115</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R28" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3281,11 +3286,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>4779</v>
+        <v>97015</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R31" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B32" t="n">
-        <v>97014</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R32" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>129450125</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450141</v>
+        <v>129450133</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>91366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656296</v>
+        <v>656452</v>
       </c>
       <c r="R19" t="n">
-        <v>6651986</v>
+        <v>6651821</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450133</v>
+        <v>129450181</v>
       </c>
       <c r="B20" t="n">
-        <v>91361</v>
+        <v>92243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656452</v>
+        <v>656449</v>
       </c>
       <c r="R20" t="n">
-        <v>6651821</v>
+        <v>6651818</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450181</v>
+        <v>129450141</v>
       </c>
       <c r="B21" t="n">
-        <v>92238</v>
+        <v>4779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656449</v>
+        <v>656296</v>
       </c>
       <c r="R21" t="n">
-        <v>6651818</v>
+        <v>6651986</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2822,32 +2822,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129450134</v>
+        <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92041</v>
+        <v>92243</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656478</v>
+        <v>656389</v>
       </c>
       <c r="R24" t="n">
-        <v>6651695</v>
+        <v>6651977</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2919,32 +2919,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129450182</v>
+        <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92238</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656389</v>
+        <v>656478</v>
       </c>
       <c r="R25" t="n">
-        <v>6651977</v>
+        <v>6651695</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B27" t="n">
-        <v>80116</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R27" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,11 +3184,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3215,32 +3210,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R28" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3286,6 +3281,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B31" t="n">
-        <v>97015</v>
+        <v>4779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R31" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>97020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R32" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1464,32 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450143</v>
+        <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656288</v>
+        <v>656478</v>
       </c>
       <c r="R10" t="n">
-        <v>6651998</v>
+        <v>6651695</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450125</v>
+        <v>129450143</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R11" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B19" t="n">
-        <v>91366</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R19" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450133</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>91366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656452</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651821</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450150</v>
+        <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>4779</v>
+        <v>97020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656444</v>
+        <v>656462</v>
       </c>
       <c r="R31" t="n">
-        <v>6651992</v>
+        <v>6651769</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129450117</v>
+        <v>129450150</v>
       </c>
       <c r="B32" t="n">
-        <v>97020</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656462</v>
+        <v>656444</v>
       </c>
       <c r="R32" t="n">
-        <v>6651769</v>
+        <v>6651992</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -2337,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450141</v>
+        <v>129450181</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656296</v>
+        <v>656449</v>
       </c>
       <c r="R19" t="n">
-        <v>6651986</v>
+        <v>6651818</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450181</v>
+        <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>92243</v>
+        <v>91366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656449</v>
+        <v>656452</v>
       </c>
       <c r="R20" t="n">
-        <v>6651818</v>
+        <v>6651821</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450133</v>
+        <v>129450141</v>
       </c>
       <c r="B21" t="n">
-        <v>91366</v>
+        <v>4779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2542,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>102306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656452</v>
+        <v>656296</v>
       </c>
       <c r="R21" t="n">
-        <v>6651821</v>
+        <v>6651986</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1464,32 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450125</v>
+        <v>129450143</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R10" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450143</v>
+        <v>129450125</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656288</v>
+        <v>656478</v>
       </c>
       <c r="R11" t="n">
-        <v>6651998</v>
+        <v>6651695</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -3113,32 +3113,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450128</v>
+        <v>129450180</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>80121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656420</v>
+        <v>656460</v>
       </c>
       <c r="R27" t="n">
-        <v>6651730</v>
+        <v>6651683</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,6 +3184,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3210,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450180</v>
+        <v>129450128</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3245,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656460</v>
+        <v>656420</v>
       </c>
       <c r="R28" t="n">
-        <v>6651683</v>
+        <v>6651730</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3281,11 +3286,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,32 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450143</v>
+        <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>91597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656288</v>
+        <v>656478</v>
       </c>
       <c r="R10" t="n">
-        <v>6651998</v>
+        <v>6651695</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450125</v>
+        <v>129450143</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R11" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129450181</v>
       </c>
       <c r="B19" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,32 +2822,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129450182</v>
+        <v>129450134</v>
       </c>
       <c r="B24" t="n">
-        <v>92243</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656389</v>
+        <v>656478</v>
       </c>
       <c r="R24" t="n">
-        <v>6651977</v>
+        <v>6651695</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2919,32 +2919,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129450134</v>
+        <v>129450182</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>92247</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656478</v>
+        <v>656389</v>
       </c>
       <c r="R25" t="n">
-        <v>6651695</v>
+        <v>6651977</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3509,7 +3509,7 @@
         <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>129450135</v>
       </c>
       <c r="B9" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>129450125</v>
       </c>
       <c r="B10" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129450118</v>
       </c>
       <c r="B12" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>129450122</v>
       </c>
       <c r="B16" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129450126</v>
       </c>
       <c r="B17" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129450181</v>
       </c>
       <c r="B19" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129450133</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2822,32 +2822,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129450134</v>
+        <v>129450182</v>
       </c>
       <c r="B24" t="n">
-        <v>92050</v>
+        <v>92249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>1339</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656478</v>
+        <v>656389</v>
       </c>
       <c r="R24" t="n">
-        <v>6651695</v>
+        <v>6651977</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2919,32 +2919,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129450182</v>
+        <v>129450134</v>
       </c>
       <c r="B25" t="n">
-        <v>92247</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656389</v>
+        <v>656478</v>
       </c>
       <c r="R25" t="n">
-        <v>6651977</v>
+        <v>6651695</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3509,7 +3509,7 @@
         <v>129450117</v>
       </c>
       <c r="B31" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>129450119</v>
       </c>
       <c r="B33" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 69711-2021 artfynd.xlsx
+++ b/artfynd/A 69711-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123037521</v>
+        <v>129450117</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällmarkerna öster om Tjyvhällsberget, Rasbo, Upl</t>
+          <t>Tjuvhällsberget ost, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656260</v>
+        <v>656462</v>
       </c>
       <c r="R2" t="n">
-        <v>6651826</v>
+        <v>6651769</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Baltasar Pinheiro</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Baltasar Pinheiro</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127482964</v>
+        <v>129450118</v>
       </c>
       <c r="B3" t="n">
-        <v>80036</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjyvhällsberget, Upl</t>
+          <t>Tjuvhällsberget ost, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656152</v>
+        <v>656384</v>
       </c>
       <c r="R3" t="n">
-        <v>6651917</v>
+        <v>6651828</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127482976</v>
+        <v>129450119</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjyvhällsberget, Upl</t>
+          <t>Tjuvhällsberget ost, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656169</v>
+        <v>656298</v>
       </c>
       <c r="R4" t="n">
-        <v>6651943</v>
+        <v>6651713</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,48 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127482989</v>
+        <v>129450121</v>
       </c>
       <c r="B5" t="n">
-        <v>91981</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjyvhällsberget, Upl</t>
+          <t>Tjuvhällsberget ost, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656150</v>
+        <v>656517</v>
       </c>
       <c r="R5" t="n">
-        <v>6651952</v>
+        <v>6651702</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,48 +1063,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127482958</v>
+        <v>129450122</v>
       </c>
       <c r="B6" t="n">
-        <v>92049</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjyvhällsberget, Upl</t>
+          <t>Tjuvhällsberget ost, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656159</v>
+        <v>656463</v>
       </c>
       <c r="R6" t="n">
-        <v>6651918</v>
+        <v>6651762</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1141,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127482975</v>
+        <v>127482957</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656161</v>
+        <v>656141</v>
       </c>
       <c r="R7" t="n">
-        <v>6651948</v>
+        <v>6651952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127482957</v>
+        <v>129450125</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,17 +1288,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjyvhällsberget, Upl</t>
+          <t>Tjuvhällsberget ost, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656141</v>
+        <v>656478</v>
       </c>
       <c r="R8" t="n">
-        <v>6651952</v>
+        <v>6651695</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1335,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129450135</v>
+        <v>129450134</v>
       </c>
       <c r="B9" t="n">
-        <v>92919</v>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656302</v>
+        <v>656478</v>
       </c>
       <c r="R9" t="n">
-        <v>6651806</v>
+        <v>6651695</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1464,48 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129450125</v>
+        <v>127482989</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjuvhällsberget ost, Upl</t>
+          <t>Tjyvhällsberget, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656478</v>
+        <v>656150</v>
       </c>
       <c r="R10" t="n">
-        <v>6651695</v>
+        <v>6651952</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1529,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129450143</v>
+        <v>129450181</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656288</v>
+        <v>656449</v>
       </c>
       <c r="R11" t="n">
-        <v>6651998</v>
+        <v>6651818</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1658,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129450118</v>
+        <v>129450182</v>
       </c>
       <c r="B12" t="n">
-        <v>97026</v>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656384</v>
+        <v>656389</v>
       </c>
       <c r="R12" t="n">
-        <v>6651828</v>
+        <v>6651977</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1755,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129450147</v>
+        <v>129450133</v>
       </c>
       <c r="B13" t="n">
-        <v>4779</v>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656424</v>
+        <v>656452</v>
       </c>
       <c r="R13" t="n">
-        <v>6651882</v>
+        <v>6651821</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1852,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129450149</v>
+        <v>127482958</v>
       </c>
       <c r="B14" t="n">
-        <v>4779</v>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjuvhällsberget ost, Upl</t>
+          <t>Tjyvhällsberget, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656408</v>
+        <v>656159</v>
       </c>
       <c r="R14" t="n">
-        <v>6651894</v>
+        <v>6651918</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1917,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1949,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129450145</v>
+        <v>129450126</v>
       </c>
       <c r="B15" t="n">
-        <v>4779</v>
+        <v>92632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656489</v>
+        <v>656381</v>
       </c>
       <c r="R15" t="n">
-        <v>6651676</v>
+        <v>6652003</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2046,48 +2033,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129450122</v>
+        <v>127482956</v>
       </c>
       <c r="B16" t="n">
-        <v>97026</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjuvhällsberget ost, Upl</t>
+          <t>Tjyvhällsberget, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656463</v>
+        <v>656248</v>
       </c>
       <c r="R16" t="n">
-        <v>6651762</v>
+        <v>6651931</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2111,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2143,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129450126</v>
+        <v>129450124</v>
       </c>
       <c r="B17" t="n">
-        <v>92317</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656381</v>
+        <v>656511</v>
       </c>
       <c r="R17" t="n">
-        <v>6652003</v>
+        <v>6651677</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2240,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129450151</v>
+        <v>129450135</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656360</v>
+        <v>656302</v>
       </c>
       <c r="R18" t="n">
-        <v>6652001</v>
+        <v>6651806</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2337,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129450181</v>
+        <v>127482964</v>
       </c>
       <c r="B19" t="n">
-        <v>92249</v>
+        <v>80336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,37 +2335,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1339</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tjuvhällsberget ost, Upl</t>
+          <t>Tjyvhällsberget, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656449</v>
+        <v>656152</v>
       </c>
       <c r="R19" t="n">
-        <v>6651818</v>
+        <v>6651917</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2402,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2434,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129450133</v>
+        <v>127482965</v>
       </c>
       <c r="B20" t="n">
-        <v>91372</v>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2445,37 +2432,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjuvhällsberget ost, Upl</t>
+          <t>Tjyvhällsberget, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656452</v>
+        <v>656114</v>
       </c>
       <c r="R20" t="n">
-        <v>6651821</v>
+        <v>6651952</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2499,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2531,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129450141</v>
+        <v>129450180</v>
       </c>
       <c r="B21" t="n">
-        <v>4779</v>
+        <v>80367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2542,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102306</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2566,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656296</v>
+        <v>656460</v>
       </c>
       <c r="R21" t="n">
-        <v>6651986</v>
+        <v>6651683</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2602,6 +2589,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2628,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129450152</v>
+        <v>123037521</v>
       </c>
       <c r="B22" t="n">
-        <v>4779</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2639,37 +2631,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tjuvhällsberget ost, Upl</t>
+          <t>Hällmarkerna öster om Tjyvhällsberget, Rasbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656331</v>
+        <v>656260</v>
       </c>
       <c r="R22" t="n">
-        <v>6651995</v>
+        <v>6651826</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2693,12 +2693,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2713,22 +2713,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Baltasar Pinheiro</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Baltasar Pinheiro</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129450144</v>
+        <v>129450140</v>
       </c>
       <c r="B23" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656452</v>
+        <v>656443</v>
       </c>
       <c r="R23" t="n">
-        <v>6651659</v>
+        <v>6651673</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129450182</v>
+        <v>129450141</v>
       </c>
       <c r="B24" t="n">
-        <v>92249</v>
+        <v>4781</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656389</v>
+        <v>656296</v>
       </c>
       <c r="R24" t="n">
-        <v>6651977</v>
+        <v>6651986</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2919,32 +2919,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129450134</v>
+        <v>129450143</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>4781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>102306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2954,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656478</v>
+        <v>656288</v>
       </c>
       <c r="R25" t="n">
-        <v>6651695</v>
+        <v>6651998</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129450146</v>
+        <v>129450144</v>
       </c>
       <c r="B26" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>656452</v>
       </c>
       <c r="R26" t="n">
-        <v>6651833</v>
+        <v>6651659</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129450180</v>
+        <v>129450145</v>
       </c>
       <c r="B27" t="n">
-        <v>80121</v>
+        <v>4781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3124,21 +3124,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656460</v>
+        <v>656489</v>
       </c>
       <c r="R27" t="n">
-        <v>6651683</v>
+        <v>6651676</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3184,11 +3184,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3215,32 +3210,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129450128</v>
+        <v>129450146</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>4781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3245,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656420</v>
+        <v>656452</v>
       </c>
       <c r="R28" t="n">
-        <v>6651730</v>
+        <v>6651833</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3312,10 +3307,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129450140</v>
+        <v>129450147</v>
       </c>
       <c r="B29" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3347,10 +3342,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>656443</v>
+        <v>656424</v>
       </c>
       <c r="R29" t="n">
-        <v>6651673</v>
+        <v>6651882</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3409,10 +3404,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129450184</v>
+        <v>129450148</v>
       </c>
       <c r="B30" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3444,10 +3439,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>656281</v>
+        <v>656416</v>
       </c>
       <c r="R30" t="n">
-        <v>6652012</v>
+        <v>6651889</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3506,32 +3501,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129450117</v>
+        <v>129450149</v>
       </c>
       <c r="B31" t="n">
-        <v>97026</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3536,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>656462</v>
+        <v>656408</v>
       </c>
       <c r="R31" t="n">
-        <v>6651769</v>
+        <v>6651894</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3606,7 +3601,7 @@
         <v>129450150</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3700,32 +3695,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129450119</v>
+        <v>129450151</v>
       </c>
       <c r="B33" t="n">
-        <v>97026</v>
+        <v>4781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3730,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>656298</v>
+        <v>656360</v>
       </c>
       <c r="R33" t="n">
-        <v>6651713</v>
+        <v>6652001</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3797,10 +3792,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129450148</v>
+        <v>129450152</v>
       </c>
       <c r="B34" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3832,10 +3827,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>656416</v>
+        <v>656331</v>
       </c>
       <c r="R34" t="n">
-        <v>6651889</v>
+        <v>6651995</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3891,6 +3886,200 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129450184</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>656281</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6652012</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129450128</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tjuvhällsberget ost, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>656420</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6651730</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
